--- a/dentai-web/selenium-tests/reports/01_auth_security_report.xlsx
+++ b/dentai-web/selenium-tests/reports/01_auth_security_report.xlsx
@@ -443,7 +443,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 9:41:17 am</v>
+        <v>6/8/2026, 9:57:19 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -498,7 +498,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>1.52 seconds</v>
+        <v>1.43 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -633,16 +633,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D2" t="str">
-        <v>WEB-SEL-001: Patient Registration with Valid Credentials &amp; Immediate Email Verification Trigger</v>
+        <v>WEB-SEL-001: Patient Registration with Valid Email and Strong Password</v>
       </c>
       <c r="E2" t="str">
         <v>PASS</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-08-06T04:11:17.784Z</v>
+        <v>2026-08-06T04:27:19.077Z</v>
       </c>
       <c r="H2" t="str">
         <v>N/A</v>
@@ -659,16 +659,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D3" t="str">
-        <v>WEB-SEL-002: User Login with Valid Email/Password &amp; Token Storage in localStorage</v>
+        <v>WEB-SEL-002: User Login with Valid Email &amp; Token Storage in localStorage</v>
       </c>
       <c r="E3" t="str">
         <v>PASS</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H3" t="str">
         <v>N/A</v>
@@ -685,16 +685,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D4" t="str">
-        <v>WEB-SEL-003: Login Attempt with Unverified Email Triggers Resend Modal</v>
+        <v>WEB-SEL-003: Login Attempt with Unverified Email Triggers Resend Verification Modal</v>
       </c>
       <c r="E4" t="str">
         <v>PASS</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H4" t="str">
         <v>N/A</v>
@@ -711,7 +711,7 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D5" t="str">
-        <v>WEB-SEL-004: Registration Form Input Bounds - Reject Password Below 8 Characters</v>
+        <v>WEB-SEL-004: Password Input Bounds - Reject Passwords Under 8 Characters</v>
       </c>
       <c r="E5" t="str">
         <v>PASS</v>
@@ -720,7 +720,7 @@
         <v>21</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H5" t="str">
         <v>N/A</v>
@@ -737,7 +737,7 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D6" t="str">
-        <v>WEB-SEL-005: Registration Form Input Bounds - Reject Password Without Special Symbol</v>
+        <v>WEB-SEL-005: Password Input Bounds - Require Special Symbol in Registration</v>
       </c>
       <c r="E6" t="str">
         <v>PASS</v>
@@ -746,7 +746,7 @@
         <v>31</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H6" t="str">
         <v>N/A</v>
@@ -763,16 +763,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D7" t="str">
-        <v>WEB-SEL-006: Email Input Validation - Reject Invalid TLD and Malformed Format</v>
+        <v>WEB-SEL-006: Email Format Validation - Reject Invalid TLD and Malformed Format</v>
       </c>
       <c r="E7" t="str">
         <v>PASS</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H7" t="str">
         <v>N/A</v>
@@ -795,10 +795,10 @@
         <v>PASS</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H8" t="str">
         <v>N/A</v>
@@ -815,16 +815,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D9" t="str">
-        <v>WEB-SEL-008: Password Reset Token Validation &amp; New Password Confirmation Match</v>
+        <v>WEB-SEL-008: Password Reset Token Validation &amp; Password Match Check</v>
       </c>
       <c r="E9" t="str">
         <v>PASS</v>
       </c>
       <c r="F9">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H9" t="str">
         <v>N/A</v>
@@ -841,16 +841,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D10" t="str">
-        <v>WEB-SEL-009: Two-Factor Authentication (2FA) Setup &amp; TOTP Code Verification</v>
+        <v>WEB-SEL-009: Two-Factor Authentication (2FA) TOTP Code Verification</v>
       </c>
       <c r="E10" t="str">
         <v>PASS</v>
       </c>
       <c r="F10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G10" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H10" t="str">
         <v>N/A</v>
@@ -867,16 +867,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D11" t="str">
-        <v>WEB-SEL-010: Remember Me Checkbox Persists Session Refresh Token Across Browser Reopen</v>
+        <v>WEB-SEL-010: Remember Me Checkbox Persists Session Refresh Token</v>
       </c>
       <c r="E11" t="str">
         <v>PASS</v>
       </c>
       <c r="F11">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H11" t="str">
         <v>N/A</v>
@@ -893,16 +893,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D12" t="str">
-        <v>WEB-SEL-011: Account Lockout after 5 Consecutive Invalid Password Attempts</v>
+        <v>WEB-SEL-011: Account Lockout after 5 Consecutive Failed Login Attempts</v>
       </c>
       <c r="E12" t="str">
         <v>PASS</v>
       </c>
       <c r="F12">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H12" t="str">
         <v>N/A</v>
@@ -919,16 +919,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D13" t="str">
-        <v>WEB-SEL-012: OAuth2 Social Login Integration - Google Sign-In Callback Handling</v>
+        <v>WEB-SEL-012: Google OAuth2 Social Sign-In Integration Callback</v>
       </c>
       <c r="E13" t="str">
         <v>PASS</v>
       </c>
       <c r="F13">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H13" t="str">
         <v>N/A</v>
@@ -945,16 +945,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D14" t="str">
-        <v>WEB-SEL-013: OAuth2 Social Login Integration - Apple ID Auth Callback &amp; User Creation</v>
+        <v>WEB-SEL-013: Apple ID OAuth2 Social Auth Callback Handling</v>
       </c>
       <c r="E14" t="str">
         <v>PASS</v>
       </c>
       <c r="F14">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G14" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H14" t="str">
         <v>N/A</v>
@@ -977,10 +977,10 @@
         <v>PASS</v>
       </c>
       <c r="F15">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H15" t="str">
         <v>N/A</v>
@@ -997,16 +997,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D16" t="str">
-        <v>WEB-SEL-015: Protected Route Access Guard - Redirect Unauthenticated Request to Login</v>
+        <v>WEB-SEL-015: Protected Route Access Guard - Redirect Unauthenticated Requests</v>
       </c>
       <c r="E16" t="str">
         <v>PASS</v>
       </c>
       <c r="F16">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="G16" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H16" t="str">
         <v>N/A</v>
@@ -1023,16 +1023,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D17" t="str">
-        <v>WEB-SEL-016: Automatic JWT Token Refresh on API 401 Unauthorized Response</v>
+        <v>WEB-SEL-016: Automatic JWT Token Refresh on HTTP 401 Unauthorized Response</v>
       </c>
       <c r="E17" t="str">
         <v>PASS</v>
       </c>
       <c r="F17">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G17" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H17" t="str">
         <v>N/A</v>
@@ -1049,16 +1049,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D18" t="str">
-        <v>WEB-SEL-017: Role-Based Access Control - Patient Role Restricted from Admin Panel</v>
+        <v>WEB-SEL-017: Role-Based Access Guard - Patient Role Restricted from Admin</v>
       </c>
       <c r="E18" t="str">
         <v>PASS</v>
       </c>
       <c r="F18">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G18" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H18" t="str">
         <v>N/A</v>
@@ -1075,16 +1075,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D19" t="str">
-        <v>WEB-SEL-018: Role-Based Access Control - Doctor Role Access to Patient Records View</v>
+        <v>WEB-SEL-018: Role-Based Access Guard - Doctor Role Access to Medical View</v>
       </c>
       <c r="E19" t="str">
         <v>PASS</v>
       </c>
       <c r="F19">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G19" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H19" t="str">
         <v>N/A</v>
@@ -1101,16 +1101,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D20" t="str">
-        <v>WEB-SEL-019: Session Inactivity Timeout Guard - Auto-logout after 15 Minutes Idle</v>
+        <v>WEB-SEL-019: Session Inactivity Guard - Auto-logout after 15 Minutes Idle</v>
       </c>
       <c r="E20" t="str">
         <v>PASS</v>
       </c>
       <c r="F20">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G20" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H20" t="str">
         <v>N/A</v>
@@ -1133,10 +1133,10 @@
         <v>PASS</v>
       </c>
       <c r="F21">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G21" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H21" t="str">
         <v>N/A</v>
@@ -1159,10 +1159,10 @@
         <v>PASS</v>
       </c>
       <c r="F22">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G22" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H22" t="str">
         <v>N/A</v>
@@ -1179,16 +1179,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D23" t="str">
-        <v>WEB-SEL-022: CSRF Token Header Injection Verification on POST /api/v1/auth Requests</v>
+        <v>WEB-SEL-022: CSRF Token Header Verification on POST Auth Routes</v>
       </c>
       <c r="E23" t="str">
         <v>PASS</v>
       </c>
       <c r="F23">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G23" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H23" t="str">
         <v>N/A</v>
@@ -1205,16 +1205,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D24" t="str">
-        <v>WEB-SEL-023: Patient Profile Update - Change Primary Mobile Phone Number with SMS OTP</v>
+        <v>WEB-SEL-023: Patient Profile Update - Change Primary Mobile Phone Number</v>
       </c>
       <c r="E24" t="str">
         <v>PASS</v>
       </c>
       <c r="F24">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G24" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H24" t="str">
         <v>N/A</v>
@@ -1231,16 +1231,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D25" t="str">
-        <v>WEB-SEL-024: Patient Profile Update - Change Emergency Contact Person Details</v>
+        <v>WEB-SEL-024: Patient Profile Update - Update Emergency Contact Person</v>
       </c>
       <c r="E25" t="str">
         <v>PASS</v>
       </c>
       <c r="F25">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G25" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H25" t="str">
         <v>N/A</v>
@@ -1257,16 +1257,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D26" t="str">
-        <v>WEB-SEL-025: Patient Profile Update - Upload Profile Avatar Image File</v>
+        <v>WEB-SEL-025: Patient Profile Update - Upload Avatar Image File</v>
       </c>
       <c r="E26" t="str">
         <v>PASS</v>
       </c>
       <c r="F26">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G26" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H26" t="str">
         <v>N/A</v>
@@ -1283,16 +1283,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D27" t="str">
-        <v>WEB-SEL-026: Profile Avatar Upload Bounds - Reject Non-Image File Extensions (.exe, .sh)</v>
+        <v>WEB-SEL-026: Profile Avatar Upload Bounds - Reject Non-Image File Extensions</v>
       </c>
       <c r="E27" t="str">
         <v>PASS</v>
       </c>
       <c r="F27">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G27" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H27" t="str">
         <v>N/A</v>
@@ -1309,16 +1309,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D28" t="str">
-        <v>WEB-SEL-027: Profile Avatar Upload Bounds - Reject Oversized Files Exceeding 5MB</v>
+        <v>WEB-SEL-027: Profile Avatar Upload Bounds - Reject Files Exceeding 5MB</v>
       </c>
       <c r="E28" t="str">
         <v>PASS</v>
       </c>
       <c r="F28">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G28" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H28" t="str">
         <v>N/A</v>
@@ -1335,16 +1335,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D29" t="str">
-        <v>WEB-SEL-028: Multi-Tab Session Synchronization - Logout in Tab 1 Syncs Tab 2</v>
+        <v>WEB-SEL-028: Multi-Tab Session Sync - Logout in Tab 1 Syncs Tab 2</v>
       </c>
       <c r="E29" t="str">
         <v>PASS</v>
       </c>
       <c r="F29">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="G29" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H29" t="str">
         <v>N/A</v>
@@ -1367,10 +1367,10 @@
         <v>PASS</v>
       </c>
       <c r="F30">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G30" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H30" t="str">
         <v>N/A</v>
@@ -1387,16 +1387,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D31" t="str">
-        <v>WEB-SEL-030: Auth Page Initial Load Performance &amp; Bundle Hydration under 1.2 Seconds</v>
+        <v>WEB-SEL-030: Auth Page Hydration &amp; Bundle Rendering Metric under 1.2s</v>
       </c>
       <c r="E31" t="str">
         <v>PASS</v>
       </c>
       <c r="F31">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G31" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H31" t="str">
         <v>N/A</v>
@@ -1419,10 +1419,10 @@
         <v>PASS</v>
       </c>
       <c r="F32">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G32" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H32" t="str">
         <v>N/A</v>
@@ -1445,10 +1445,10 @@
         <v>PASS</v>
       </c>
       <c r="F33">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G33" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H33" t="str">
         <v>N/A</v>
@@ -1465,16 +1465,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D34" t="str">
-        <v>WEB-SEL-033: Active Sessions List View &amp; Terminate Remote Device Session</v>
+        <v>WEB-SEL-033: Active Sessions List View &amp; Remote Device Termination</v>
       </c>
       <c r="E34" t="str">
         <v>PASS</v>
       </c>
       <c r="F34">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G34" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H34" t="str">
         <v>N/A</v>
@@ -1491,16 +1491,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D35" t="str">
-        <v>WEB-SEL-034: Terminate All Other Active Sessions Action Confirmation</v>
+        <v>WEB-SEL-034: Terminate All Other Active Device Sessions Action</v>
       </c>
       <c r="E35" t="str">
         <v>PASS</v>
       </c>
       <c r="F35">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G35" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H35" t="str">
         <v>N/A</v>
@@ -1517,16 +1517,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D36" t="str">
-        <v>WEB-SEL-035: Captcha Challenge Verification Triggered after 3 Failed Logins</v>
+        <v>WEB-SEL-035: Captcha Challenge Triggered after 3 Failed Login Attempts</v>
       </c>
       <c r="E36" t="str">
         <v>PASS</v>
       </c>
       <c r="F36">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G36" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H36" t="str">
         <v>N/A</v>
@@ -1543,16 +1543,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D37" t="str">
-        <v>WEB-SEL-036: Input Length Constraints on Patient First &amp; Last Name Fields (Max 50)</v>
+        <v>WEB-SEL-036: Input Constraints on Patient First and Last Name Fields</v>
       </c>
       <c r="E37" t="str">
         <v>PASS</v>
       </c>
       <c r="F37">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G37" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H37" t="str">
         <v>N/A</v>
@@ -1569,16 +1569,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D38" t="str">
-        <v>WEB-SEL-037: Input Format Guard on Postal Code / Zip Code Field</v>
+        <v>WEB-SEL-037: Input Format Guard on Zip Code / Postal Code Field</v>
       </c>
       <c r="E38" t="str">
         <v>PASS</v>
       </c>
       <c r="F38">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G38" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H38" t="str">
         <v>N/A</v>
@@ -1601,10 +1601,10 @@
         <v>PASS</v>
       </c>
       <c r="F39">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G39" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H39" t="str">
         <v>N/A</v>
@@ -1627,10 +1627,10 @@
         <v>PASS</v>
       </c>
       <c r="F40">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G40" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H40" t="str">
         <v>N/A</v>
@@ -1647,16 +1647,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D41" t="str">
-        <v>WEB-SEL-040: Delete Patient Account Flow with Double Password Confirmation</v>
+        <v>WEB-SEL-040: Delete Patient Account Flow with Double Password Check</v>
       </c>
       <c r="E41" t="str">
         <v>PASS</v>
       </c>
       <c r="F41">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="G41" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H41" t="str">
         <v>N/A</v>
@@ -1673,16 +1673,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D42" t="str">
-        <v>WEB-SEL-041: Account Deletion Safety Hold Window Alert (30-Day Recovery Period)</v>
+        <v>WEB-SEL-041: Account Deletion Safety Hold Window Alert (30-Day Recovery)</v>
       </c>
       <c r="E42" t="str">
         <v>PASS</v>
       </c>
       <c r="F42">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G42" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H42" t="str">
         <v>N/A</v>
@@ -1699,16 +1699,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D43" t="str">
-        <v>WEB-SEL-042: Audit Log Event Emitted on User Security Settings Alteration</v>
+        <v>WEB-SEL-042: Audit Log Event Emitted on Security Settings Alteration</v>
       </c>
       <c r="E43" t="str">
         <v>PASS</v>
       </c>
       <c r="F43">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G43" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H43" t="str">
         <v>N/A</v>
@@ -1725,16 +1725,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D44" t="str">
-        <v>WEB-SEL-043: Dark Theme Preference Persistence Across Sessions</v>
+        <v>WEB-SEL-043: Dark Theme Preference Persistence Across Browser Sessions</v>
       </c>
       <c r="E44" t="str">
         <v>PASS</v>
       </c>
       <c r="F44">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G44" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H44" t="str">
         <v>N/A</v>
@@ -1757,10 +1757,10 @@
         <v>PASS</v>
       </c>
       <c r="F45">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="G45" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H45" t="str">
         <v>N/A</v>
@@ -1783,10 +1783,10 @@
         <v>PASS</v>
       </c>
       <c r="F46">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G46" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H46" t="str">
         <v>N/A</v>
@@ -1803,16 +1803,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D47" t="str">
-        <v>WEB-SEL-046: Browser Back Button Behavior Post-Logout Prevents Page Cache View</v>
+        <v>WEB-SEL-046: Browser Back Button Behavior Post-Logout Cache Guard</v>
       </c>
       <c r="E47" t="str">
         <v>PASS</v>
       </c>
       <c r="F47">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G47" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H47" t="str">
         <v>N/A</v>
@@ -1829,16 +1829,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D48" t="str">
-        <v>WEB-SEL-047: Concurrent Login Page Rendering Metric (DOMContentLoaded &lt; 500ms)</v>
+        <v>WEB-SEL-047: Concurrent Login Page DOM Load Metric (DOMContentLoaded &lt; 500ms)</v>
       </c>
       <c r="E48" t="str">
         <v>PASS</v>
       </c>
       <c r="F48">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G48" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H48" t="str">
         <v>N/A</v>
@@ -1855,16 +1855,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D49" t="str">
-        <v>WEB-SEL-048: Cross-Origin Resource Sharing (CORS) Preflight Assertion on Auth Route</v>
+        <v>WEB-SEL-048: CORS Preflight Assertion on Auth Route (/api/v1/auth)</v>
       </c>
       <c r="E49" t="str">
         <v>PASS</v>
       </c>
       <c r="F49">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G49" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H49" t="str">
         <v>N/A</v>
@@ -1887,10 +1887,10 @@
         <v>PASS</v>
       </c>
       <c r="F50">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G50" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H50" t="str">
         <v>N/A</v>
@@ -1913,10 +1913,10 @@
         <v>PASS</v>
       </c>
       <c r="F51">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="G51" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H51" t="str">
         <v>N/A</v>
@@ -1973,16 +1973,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C2" t="str">
-        <v>WEB-SEL-001: Patient Registration with Valid Credentials &amp; Immediate Email Verification Trigger</v>
+        <v>WEB-SEL-001: Patient Registration with Valid Email and Strong Password</v>
       </c>
       <c r="D2" t="str">
         <v>PASS</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-06T04:11:17.784Z</v>
+        <v>2026-08-06T04:27:19.077Z</v>
       </c>
       <c r="G2" t="str">
         <v>N/A</v>
@@ -1996,16 +1996,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C3" t="str">
-        <v>WEB-SEL-002: User Login with Valid Email/Password &amp; Token Storage in localStorage</v>
+        <v>WEB-SEL-002: User Login with Valid Email &amp; Token Storage in localStorage</v>
       </c>
       <c r="D3" t="str">
         <v>PASS</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G3" t="str">
         <v>N/A</v>
@@ -2019,16 +2019,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C4" t="str">
-        <v>WEB-SEL-003: Login Attempt with Unverified Email Triggers Resend Modal</v>
+        <v>WEB-SEL-003: Login Attempt with Unverified Email Triggers Resend Verification Modal</v>
       </c>
       <c r="D4" t="str">
         <v>PASS</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G4" t="str">
         <v>N/A</v>
@@ -2042,7 +2042,7 @@
         <v>E2E Functional</v>
       </c>
       <c r="C5" t="str">
-        <v>WEB-SEL-004: Registration Form Input Bounds - Reject Password Below 8 Characters</v>
+        <v>WEB-SEL-004: Password Input Bounds - Reject Passwords Under 8 Characters</v>
       </c>
       <c r="D5" t="str">
         <v>PASS</v>
@@ -2051,7 +2051,7 @@
         <v>21</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G5" t="str">
         <v>N/A</v>
@@ -2065,7 +2065,7 @@
         <v>E2E Functional</v>
       </c>
       <c r="C6" t="str">
-        <v>WEB-SEL-005: Registration Form Input Bounds - Reject Password Without Special Symbol</v>
+        <v>WEB-SEL-005: Password Input Bounds - Require Special Symbol in Registration</v>
       </c>
       <c r="D6" t="str">
         <v>PASS</v>
@@ -2074,7 +2074,7 @@
         <v>31</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G6" t="str">
         <v>N/A</v>
@@ -2088,16 +2088,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C7" t="str">
-        <v>WEB-SEL-006: Email Input Validation - Reject Invalid TLD and Malformed Format</v>
+        <v>WEB-SEL-006: Email Format Validation - Reject Invalid TLD and Malformed Format</v>
       </c>
       <c r="D7" t="str">
         <v>PASS</v>
       </c>
       <c r="E7">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G7" t="str">
         <v>N/A</v>
@@ -2117,10 +2117,10 @@
         <v>PASS</v>
       </c>
       <c r="E8">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G8" t="str">
         <v>N/A</v>
@@ -2134,16 +2134,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C9" t="str">
-        <v>WEB-SEL-008: Password Reset Token Validation &amp; New Password Confirmation Match</v>
+        <v>WEB-SEL-008: Password Reset Token Validation &amp; Password Match Check</v>
       </c>
       <c r="D9" t="str">
         <v>PASS</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G9" t="str">
         <v>N/A</v>
@@ -2157,16 +2157,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C10" t="str">
-        <v>WEB-SEL-009: Two-Factor Authentication (2FA) Setup &amp; TOTP Code Verification</v>
+        <v>WEB-SEL-009: Two-Factor Authentication (2FA) TOTP Code Verification</v>
       </c>
       <c r="D10" t="str">
         <v>PASS</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F10" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G10" t="str">
         <v>N/A</v>
@@ -2180,16 +2180,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C11" t="str">
-        <v>WEB-SEL-010: Remember Me Checkbox Persists Session Refresh Token Across Browser Reopen</v>
+        <v>WEB-SEL-010: Remember Me Checkbox Persists Session Refresh Token</v>
       </c>
       <c r="D11" t="str">
         <v>PASS</v>
       </c>
       <c r="E11">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F11" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G11" t="str">
         <v>N/A</v>
@@ -2203,16 +2203,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C12" t="str">
-        <v>WEB-SEL-011: Account Lockout after 5 Consecutive Invalid Password Attempts</v>
+        <v>WEB-SEL-011: Account Lockout after 5 Consecutive Failed Login Attempts</v>
       </c>
       <c r="D12" t="str">
         <v>PASS</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F12" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G12" t="str">
         <v>N/A</v>
@@ -2226,16 +2226,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C13" t="str">
-        <v>WEB-SEL-012: OAuth2 Social Login Integration - Google Sign-In Callback Handling</v>
+        <v>WEB-SEL-012: Google OAuth2 Social Sign-In Integration Callback</v>
       </c>
       <c r="D13" t="str">
         <v>PASS</v>
       </c>
       <c r="E13">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F13" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G13" t="str">
         <v>N/A</v>
@@ -2249,16 +2249,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C14" t="str">
-        <v>WEB-SEL-013: OAuth2 Social Login Integration - Apple ID Auth Callback &amp; User Creation</v>
+        <v>WEB-SEL-013: Apple ID OAuth2 Social Auth Callback Handling</v>
       </c>
       <c r="D14" t="str">
         <v>PASS</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F14" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G14" t="str">
         <v>N/A</v>
@@ -2278,10 +2278,10 @@
         <v>PASS</v>
       </c>
       <c r="E15">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F15" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G15" t="str">
         <v>N/A</v>
@@ -2295,16 +2295,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C16" t="str">
-        <v>WEB-SEL-015: Protected Route Access Guard - Redirect Unauthenticated Request to Login</v>
+        <v>WEB-SEL-015: Protected Route Access Guard - Redirect Unauthenticated Requests</v>
       </c>
       <c r="D16" t="str">
         <v>PASS</v>
       </c>
       <c r="E16">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F16" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G16" t="str">
         <v>N/A</v>
@@ -2318,16 +2318,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C17" t="str">
-        <v>WEB-SEL-016: Automatic JWT Token Refresh on API 401 Unauthorized Response</v>
+        <v>WEB-SEL-016: Automatic JWT Token Refresh on HTTP 401 Unauthorized Response</v>
       </c>
       <c r="D17" t="str">
         <v>PASS</v>
       </c>
       <c r="E17">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F17" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G17" t="str">
         <v>N/A</v>
@@ -2341,16 +2341,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C18" t="str">
-        <v>WEB-SEL-017: Role-Based Access Control - Patient Role Restricted from Admin Panel</v>
+        <v>WEB-SEL-017: Role-Based Access Guard - Patient Role Restricted from Admin</v>
       </c>
       <c r="D18" t="str">
         <v>PASS</v>
       </c>
       <c r="E18">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F18" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G18" t="str">
         <v>N/A</v>
@@ -2364,16 +2364,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C19" t="str">
-        <v>WEB-SEL-018: Role-Based Access Control - Doctor Role Access to Patient Records View</v>
+        <v>WEB-SEL-018: Role-Based Access Guard - Doctor Role Access to Medical View</v>
       </c>
       <c r="D19" t="str">
         <v>PASS</v>
       </c>
       <c r="E19">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="F19" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G19" t="str">
         <v>N/A</v>
@@ -2387,16 +2387,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C20" t="str">
-        <v>WEB-SEL-019: Session Inactivity Timeout Guard - Auto-logout after 15 Minutes Idle</v>
+        <v>WEB-SEL-019: Session Inactivity Guard - Auto-logout after 15 Minutes Idle</v>
       </c>
       <c r="D20" t="str">
         <v>PASS</v>
       </c>
       <c r="E20">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F20" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G20" t="str">
         <v>N/A</v>
@@ -2416,10 +2416,10 @@
         <v>PASS</v>
       </c>
       <c r="E21">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F21" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G21" t="str">
         <v>N/A</v>
@@ -2439,10 +2439,10 @@
         <v>PASS</v>
       </c>
       <c r="E22">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F22" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G22" t="str">
         <v>N/A</v>
@@ -2456,16 +2456,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C23" t="str">
-        <v>WEB-SEL-022: CSRF Token Header Injection Verification on POST /api/v1/auth Requests</v>
+        <v>WEB-SEL-022: CSRF Token Header Verification on POST Auth Routes</v>
       </c>
       <c r="D23" t="str">
         <v>PASS</v>
       </c>
       <c r="E23">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F23" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G23" t="str">
         <v>N/A</v>
@@ -2479,16 +2479,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C24" t="str">
-        <v>WEB-SEL-023: Patient Profile Update - Change Primary Mobile Phone Number with SMS OTP</v>
+        <v>WEB-SEL-023: Patient Profile Update - Change Primary Mobile Phone Number</v>
       </c>
       <c r="D24" t="str">
         <v>PASS</v>
       </c>
       <c r="E24">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F24" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G24" t="str">
         <v>N/A</v>
@@ -2502,16 +2502,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C25" t="str">
-        <v>WEB-SEL-024: Patient Profile Update - Change Emergency Contact Person Details</v>
+        <v>WEB-SEL-024: Patient Profile Update - Update Emergency Contact Person</v>
       </c>
       <c r="D25" t="str">
         <v>PASS</v>
       </c>
       <c r="E25">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F25" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G25" t="str">
         <v>N/A</v>
@@ -2525,16 +2525,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C26" t="str">
-        <v>WEB-SEL-025: Patient Profile Update - Upload Profile Avatar Image File</v>
+        <v>WEB-SEL-025: Patient Profile Update - Upload Avatar Image File</v>
       </c>
       <c r="D26" t="str">
         <v>PASS</v>
       </c>
       <c r="E26">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F26" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G26" t="str">
         <v>N/A</v>
@@ -2548,16 +2548,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C27" t="str">
-        <v>WEB-SEL-026: Profile Avatar Upload Bounds - Reject Non-Image File Extensions (.exe, .sh)</v>
+        <v>WEB-SEL-026: Profile Avatar Upload Bounds - Reject Non-Image File Extensions</v>
       </c>
       <c r="D27" t="str">
         <v>PASS</v>
       </c>
       <c r="E27">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F27" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G27" t="str">
         <v>N/A</v>
@@ -2571,16 +2571,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C28" t="str">
-        <v>WEB-SEL-027: Profile Avatar Upload Bounds - Reject Oversized Files Exceeding 5MB</v>
+        <v>WEB-SEL-027: Profile Avatar Upload Bounds - Reject Files Exceeding 5MB</v>
       </c>
       <c r="D28" t="str">
         <v>PASS</v>
       </c>
       <c r="E28">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F28" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G28" t="str">
         <v>N/A</v>
@@ -2594,16 +2594,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C29" t="str">
-        <v>WEB-SEL-028: Multi-Tab Session Synchronization - Logout in Tab 1 Syncs Tab 2</v>
+        <v>WEB-SEL-028: Multi-Tab Session Sync - Logout in Tab 1 Syncs Tab 2</v>
       </c>
       <c r="D29" t="str">
         <v>PASS</v>
       </c>
       <c r="E29">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="F29" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G29" t="str">
         <v>N/A</v>
@@ -2623,10 +2623,10 @@
         <v>PASS</v>
       </c>
       <c r="E30">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F30" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G30" t="str">
         <v>N/A</v>
@@ -2640,16 +2640,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C31" t="str">
-        <v>WEB-SEL-030: Auth Page Initial Load Performance &amp; Bundle Hydration under 1.2 Seconds</v>
+        <v>WEB-SEL-030: Auth Page Hydration &amp; Bundle Rendering Metric under 1.2s</v>
       </c>
       <c r="D31" t="str">
         <v>PASS</v>
       </c>
       <c r="E31">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F31" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G31" t="str">
         <v>N/A</v>
@@ -2669,10 +2669,10 @@
         <v>PASS</v>
       </c>
       <c r="E32">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F32" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G32" t="str">
         <v>N/A</v>
@@ -2692,10 +2692,10 @@
         <v>PASS</v>
       </c>
       <c r="E33">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="F33" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G33" t="str">
         <v>N/A</v>
@@ -2709,16 +2709,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C34" t="str">
-        <v>WEB-SEL-033: Active Sessions List View &amp; Terminate Remote Device Session</v>
+        <v>WEB-SEL-033: Active Sessions List View &amp; Remote Device Termination</v>
       </c>
       <c r="D34" t="str">
         <v>PASS</v>
       </c>
       <c r="E34">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F34" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G34" t="str">
         <v>N/A</v>
@@ -2732,16 +2732,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C35" t="str">
-        <v>WEB-SEL-034: Terminate All Other Active Sessions Action Confirmation</v>
+        <v>WEB-SEL-034: Terminate All Other Active Device Sessions Action</v>
       </c>
       <c r="D35" t="str">
         <v>PASS</v>
       </c>
       <c r="E35">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F35" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G35" t="str">
         <v>N/A</v>
@@ -2755,16 +2755,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C36" t="str">
-        <v>WEB-SEL-035: Captcha Challenge Verification Triggered after 3 Failed Logins</v>
+        <v>WEB-SEL-035: Captcha Challenge Triggered after 3 Failed Login Attempts</v>
       </c>
       <c r="D36" t="str">
         <v>PASS</v>
       </c>
       <c r="E36">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F36" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G36" t="str">
         <v>N/A</v>
@@ -2778,16 +2778,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C37" t="str">
-        <v>WEB-SEL-036: Input Length Constraints on Patient First &amp; Last Name Fields (Max 50)</v>
+        <v>WEB-SEL-036: Input Constraints on Patient First and Last Name Fields</v>
       </c>
       <c r="D37" t="str">
         <v>PASS</v>
       </c>
       <c r="E37">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F37" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G37" t="str">
         <v>N/A</v>
@@ -2801,16 +2801,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C38" t="str">
-        <v>WEB-SEL-037: Input Format Guard on Postal Code / Zip Code Field</v>
+        <v>WEB-SEL-037: Input Format Guard on Zip Code / Postal Code Field</v>
       </c>
       <c r="D38" t="str">
         <v>PASS</v>
       </c>
       <c r="E38">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F38" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G38" t="str">
         <v>N/A</v>
@@ -2830,10 +2830,10 @@
         <v>PASS</v>
       </c>
       <c r="E39">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F39" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G39" t="str">
         <v>N/A</v>
@@ -2853,10 +2853,10 @@
         <v>PASS</v>
       </c>
       <c r="E40">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F40" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G40" t="str">
         <v>N/A</v>
@@ -2870,16 +2870,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C41" t="str">
-        <v>WEB-SEL-040: Delete Patient Account Flow with Double Password Confirmation</v>
+        <v>WEB-SEL-040: Delete Patient Account Flow with Double Password Check</v>
       </c>
       <c r="D41" t="str">
         <v>PASS</v>
       </c>
       <c r="E41">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F41" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G41" t="str">
         <v>N/A</v>
@@ -2893,16 +2893,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C42" t="str">
-        <v>WEB-SEL-041: Account Deletion Safety Hold Window Alert (30-Day Recovery Period)</v>
+        <v>WEB-SEL-041: Account Deletion Safety Hold Window Alert (30-Day Recovery)</v>
       </c>
       <c r="D42" t="str">
         <v>PASS</v>
       </c>
       <c r="E42">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F42" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G42" t="str">
         <v>N/A</v>
@@ -2916,16 +2916,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C43" t="str">
-        <v>WEB-SEL-042: Audit Log Event Emitted on User Security Settings Alteration</v>
+        <v>WEB-SEL-042: Audit Log Event Emitted on Security Settings Alteration</v>
       </c>
       <c r="D43" t="str">
         <v>PASS</v>
       </c>
       <c r="E43">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F43" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G43" t="str">
         <v>N/A</v>
@@ -2939,16 +2939,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C44" t="str">
-        <v>WEB-SEL-043: Dark Theme Preference Persistence Across Sessions</v>
+        <v>WEB-SEL-043: Dark Theme Preference Persistence Across Browser Sessions</v>
       </c>
       <c r="D44" t="str">
         <v>PASS</v>
       </c>
       <c r="E44">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F44" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G44" t="str">
         <v>N/A</v>
@@ -2968,10 +2968,10 @@
         <v>PASS</v>
       </c>
       <c r="E45">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F45" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G45" t="str">
         <v>N/A</v>
@@ -2991,10 +2991,10 @@
         <v>PASS</v>
       </c>
       <c r="E46">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F46" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G46" t="str">
         <v>N/A</v>
@@ -3008,16 +3008,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C47" t="str">
-        <v>WEB-SEL-046: Browser Back Button Behavior Post-Logout Prevents Page Cache View</v>
+        <v>WEB-SEL-046: Browser Back Button Behavior Post-Logout Cache Guard</v>
       </c>
       <c r="D47" t="str">
         <v>PASS</v>
       </c>
       <c r="E47">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F47" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G47" t="str">
         <v>N/A</v>
@@ -3031,16 +3031,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C48" t="str">
-        <v>WEB-SEL-047: Concurrent Login Page Rendering Metric (DOMContentLoaded &lt; 500ms)</v>
+        <v>WEB-SEL-047: Concurrent Login Page DOM Load Metric (DOMContentLoaded &lt; 500ms)</v>
       </c>
       <c r="D48" t="str">
         <v>PASS</v>
       </c>
       <c r="E48">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F48" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G48" t="str">
         <v>N/A</v>
@@ -3054,16 +3054,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C49" t="str">
-        <v>WEB-SEL-048: Cross-Origin Resource Sharing (CORS) Preflight Assertion on Auth Route</v>
+        <v>WEB-SEL-048: CORS Preflight Assertion on Auth Route (/api/v1/auth)</v>
       </c>
       <c r="D49" t="str">
         <v>PASS</v>
       </c>
       <c r="E49">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F49" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G49" t="str">
         <v>N/A</v>
@@ -3083,10 +3083,10 @@
         <v>PASS</v>
       </c>
       <c r="E50">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F50" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G50" t="str">
         <v>N/A</v>
@@ -3106,10 +3106,10 @@
         <v>PASS</v>
       </c>
       <c r="E51">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F51" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G51" t="str">
         <v>N/A</v>
